--- a/simulation_data/tuesday_afternoon.xlsx
+++ b/simulation_data/tuesday_afternoon.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="111">
   <si>
     <t>Arrival</t>
   </si>
@@ -254,6 +254,99 @@
   </si>
   <si>
     <t>13:56:00</t>
+  </si>
+  <si>
+    <t>00:00:00</t>
+  </si>
+  <si>
+    <t>00:00:23</t>
+  </si>
+  <si>
+    <t>00:00:03</t>
+  </si>
+  <si>
+    <t>00:00:19</t>
+  </si>
+  <si>
+    <t>00:00:26</t>
+  </si>
+  <si>
+    <t>00:00:25</t>
+  </si>
+  <si>
+    <t>00:00:10</t>
+  </si>
+  <si>
+    <t>00:00:14</t>
+  </si>
+  <si>
+    <t>00:00:31</t>
+  </si>
+  <si>
+    <t>00:00:21</t>
+  </si>
+  <si>
+    <t>00:00:12</t>
+  </si>
+  <si>
+    <t>00:00:27</t>
+  </si>
+  <si>
+    <t>00:00:13</t>
+  </si>
+  <si>
+    <t>00:00:36</t>
+  </si>
+  <si>
+    <t>00:00:28</t>
+  </si>
+  <si>
+    <t>00:00:33</t>
+  </si>
+  <si>
+    <t>00:00:37</t>
+  </si>
+  <si>
+    <t>00:00:15</t>
+  </si>
+  <si>
+    <t>00:00:29</t>
+  </si>
+  <si>
+    <t>00:00:06</t>
+  </si>
+  <si>
+    <t>00:00:24</t>
+  </si>
+  <si>
+    <t>00:00:11</t>
+  </si>
+  <si>
+    <t>00:00:20</t>
+  </si>
+  <si>
+    <t>00:00:34</t>
+  </si>
+  <si>
+    <t>00:00:30</t>
+  </si>
+  <si>
+    <t>00:00:17</t>
+  </si>
+  <si>
+    <t>00:00:16</t>
+  </si>
+  <si>
+    <t>00:00:07</t>
+  </si>
+  <si>
+    <t>00:00:32</t>
+  </si>
+  <si>
+    <t>00:00:08</t>
+  </si>
+  <si>
+    <t>00:00:22</t>
   </si>
 </sst>
 </file>
@@ -641,11 +734,11 @@
       <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
+      <c r="D2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E2" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -658,11 +751,11 @@
       <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
+      <c r="D3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -675,11 +768,11 @@
       <c r="C4" t="s">
         <v>8</v>
       </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
+      <c r="D4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -692,11 +785,11 @@
       <c r="C5" t="s">
         <v>8</v>
       </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
+      <c r="D5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -709,11 +802,11 @@
       <c r="C6" t="s">
         <v>63</v>
       </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
+      <c r="D6" t="s">
+        <v>83</v>
+      </c>
+      <c r="E6" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -726,11 +819,11 @@
       <c r="C7" t="s">
         <v>63</v>
       </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
+      <c r="D7" t="s">
+        <v>84</v>
+      </c>
+      <c r="E7" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -743,11 +836,11 @@
       <c r="C8" t="s">
         <v>63</v>
       </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
+      <c r="D8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -760,11 +853,11 @@
       <c r="C9" t="s">
         <v>11</v>
       </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
+      <c r="D9" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -777,11 +870,11 @@
       <c r="C10" t="s">
         <v>63</v>
       </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
+      <c r="D10" t="s">
+        <v>80</v>
+      </c>
+      <c r="E10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -794,11 +887,11 @@
       <c r="C11" t="s">
         <v>11</v>
       </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
+      <c r="D11" t="s">
+        <v>80</v>
+      </c>
+      <c r="E11" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -811,11 +904,11 @@
       <c r="C12" t="s">
         <v>11</v>
       </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
+      <c r="D12" t="s">
+        <v>80</v>
+      </c>
+      <c r="E12" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -828,11 +921,11 @@
       <c r="C13" t="s">
         <v>13</v>
       </c>
-      <c r="D13">
-        <v>2</v>
-      </c>
-      <c r="E13">
-        <v>1</v>
+      <c r="D13" t="s">
+        <v>82</v>
+      </c>
+      <c r="E13" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -845,11 +938,11 @@
       <c r="C14" t="s">
         <v>64</v>
       </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14">
-        <v>2</v>
+      <c r="D14" t="s">
+        <v>85</v>
+      </c>
+      <c r="E14" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -862,11 +955,11 @@
       <c r="C15" t="s">
         <v>64</v>
       </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15">
-        <v>1</v>
+      <c r="D15" t="s">
+        <v>86</v>
+      </c>
+      <c r="E15" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -879,11 +972,11 @@
       <c r="C16" t="s">
         <v>15</v>
       </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16">
-        <v>1</v>
+      <c r="D16" t="s">
+        <v>82</v>
+      </c>
+      <c r="E16" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -896,11 +989,11 @@
       <c r="C17" t="s">
         <v>76</v>
       </c>
-      <c r="D17">
-        <v>2</v>
-      </c>
-      <c r="E17">
-        <v>1</v>
+      <c r="D17" t="s">
+        <v>82</v>
+      </c>
+      <c r="E17" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -913,11 +1006,11 @@
       <c r="C18" t="s">
         <v>65</v>
       </c>
-      <c r="D18">
-        <v>2</v>
-      </c>
-      <c r="E18">
-        <v>1</v>
+      <c r="D18" t="s">
+        <v>82</v>
+      </c>
+      <c r="E18" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -930,11 +1023,11 @@
       <c r="C19" t="s">
         <v>17</v>
       </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>1</v>
+      <c r="D19" t="s">
+        <v>80</v>
+      </c>
+      <c r="E19" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -947,11 +1040,11 @@
       <c r="C20" t="s">
         <v>18</v>
       </c>
-      <c r="D20">
-        <v>2</v>
-      </c>
-      <c r="E20">
-        <v>1</v>
+      <c r="D20" t="s">
+        <v>87</v>
+      </c>
+      <c r="E20" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -964,11 +1057,11 @@
       <c r="C21" t="s">
         <v>66</v>
       </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-      <c r="E21">
-        <v>2</v>
+      <c r="D21" t="s">
+        <v>88</v>
+      </c>
+      <c r="E21" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -981,11 +1074,11 @@
       <c r="C22" t="s">
         <v>66</v>
       </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22">
-        <v>2</v>
+      <c r="D22" t="s">
+        <v>80</v>
+      </c>
+      <c r="E22" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -998,11 +1091,11 @@
       <c r="C23" t="s">
         <v>20</v>
       </c>
-      <c r="D23">
-        <v>1</v>
-      </c>
-      <c r="E23">
-        <v>1</v>
+      <c r="D23" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1015,11 +1108,11 @@
       <c r="C24" t="s">
         <v>20</v>
       </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
-      <c r="E24">
-        <v>1</v>
+      <c r="D24" t="s">
+        <v>80</v>
+      </c>
+      <c r="E24" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1032,11 +1125,11 @@
       <c r="C25" t="s">
         <v>21</v>
       </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
-      <c r="E25">
-        <v>1</v>
+      <c r="D25" t="s">
+        <v>80</v>
+      </c>
+      <c r="E25" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1049,11 +1142,11 @@
       <c r="C26" t="s">
         <v>22</v>
       </c>
-      <c r="D26">
-        <v>2</v>
-      </c>
-      <c r="E26">
-        <v>2</v>
+      <c r="D26" t="s">
+        <v>82</v>
+      </c>
+      <c r="E26" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1066,11 +1159,11 @@
       <c r="C27" t="s">
         <v>23</v>
       </c>
-      <c r="D27">
-        <v>1</v>
-      </c>
-      <c r="E27">
-        <v>1</v>
+      <c r="D27" t="s">
+        <v>82</v>
+      </c>
+      <c r="E27" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1083,11 +1176,11 @@
       <c r="C28" t="s">
         <v>24</v>
       </c>
-      <c r="D28">
-        <v>0</v>
-      </c>
-      <c r="E28">
-        <v>1</v>
+      <c r="D28" t="s">
+        <v>80</v>
+      </c>
+      <c r="E28" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1100,11 +1193,11 @@
       <c r="C29" t="s">
         <v>24</v>
       </c>
-      <c r="D29">
-        <v>0</v>
-      </c>
-      <c r="E29">
-        <v>1</v>
+      <c r="D29" t="s">
+        <v>80</v>
+      </c>
+      <c r="E29" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1117,11 +1210,11 @@
       <c r="C30" t="s">
         <v>24</v>
       </c>
-      <c r="D30">
-        <v>1</v>
-      </c>
-      <c r="E30">
-        <v>1</v>
+      <c r="D30" t="s">
+        <v>82</v>
+      </c>
+      <c r="E30" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1134,11 +1227,11 @@
       <c r="C31" t="s">
         <v>24</v>
       </c>
-      <c r="D31">
-        <v>0</v>
-      </c>
-      <c r="E31">
-        <v>1</v>
+      <c r="D31" t="s">
+        <v>80</v>
+      </c>
+      <c r="E31" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1151,11 +1244,11 @@
       <c r="C32" t="s">
         <v>25</v>
       </c>
-      <c r="D32">
-        <v>1</v>
-      </c>
-      <c r="E32">
-        <v>1</v>
+      <c r="D32" t="s">
+        <v>89</v>
+      </c>
+      <c r="E32" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1168,11 +1261,11 @@
       <c r="C33" t="s">
         <v>26</v>
       </c>
-      <c r="D33">
-        <v>1</v>
-      </c>
-      <c r="E33">
-        <v>1</v>
+      <c r="D33" t="s">
+        <v>82</v>
+      </c>
+      <c r="E33" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1185,11 +1278,11 @@
       <c r="C34" t="s">
         <v>26</v>
       </c>
-      <c r="D34">
-        <v>0</v>
-      </c>
-      <c r="E34">
-        <v>1</v>
+      <c r="D34" t="s">
+        <v>80</v>
+      </c>
+      <c r="E34" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1202,11 +1295,11 @@
       <c r="C35" t="s">
         <v>27</v>
       </c>
-      <c r="D35">
-        <v>0</v>
-      </c>
-      <c r="E35">
-        <v>1</v>
+      <c r="D35" t="s">
+        <v>80</v>
+      </c>
+      <c r="E35" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -1219,11 +1312,11 @@
       <c r="C36" t="s">
         <v>67</v>
       </c>
-      <c r="D36">
-        <v>1</v>
-      </c>
-      <c r="E36">
-        <v>2</v>
+      <c r="D36" t="s">
+        <v>82</v>
+      </c>
+      <c r="E36" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -1236,11 +1329,11 @@
       <c r="C37" t="s">
         <v>29</v>
       </c>
-      <c r="D37">
-        <v>1</v>
-      </c>
-      <c r="E37">
-        <v>3</v>
+      <c r="D37" t="s">
+        <v>82</v>
+      </c>
+      <c r="E37" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1253,11 +1346,11 @@
       <c r="C38" t="s">
         <v>67</v>
       </c>
-      <c r="D38">
-        <v>1</v>
-      </c>
-      <c r="E38">
-        <v>1</v>
+      <c r="D38" t="s">
+        <v>83</v>
+      </c>
+      <c r="E38" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1270,11 +1363,11 @@
       <c r="C39" t="s">
         <v>67</v>
       </c>
-      <c r="D39">
-        <v>1</v>
-      </c>
-      <c r="E39">
-        <v>1</v>
+      <c r="D39" t="s">
+        <v>82</v>
+      </c>
+      <c r="E39" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1287,11 +1380,11 @@
       <c r="C40" t="s">
         <v>29</v>
       </c>
-      <c r="D40">
-        <v>0</v>
-      </c>
-      <c r="E40">
-        <v>1</v>
+      <c r="D40" t="s">
+        <v>80</v>
+      </c>
+      <c r="E40" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1304,11 +1397,11 @@
       <c r="C41" t="s">
         <v>30</v>
       </c>
-      <c r="D41">
-        <v>0</v>
-      </c>
-      <c r="E41">
-        <v>1</v>
+      <c r="D41" t="s">
+        <v>80</v>
+      </c>
+      <c r="E41" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1321,11 +1414,11 @@
       <c r="C42" t="s">
         <v>68</v>
       </c>
-      <c r="D42">
-        <v>0</v>
-      </c>
-      <c r="E42">
-        <v>2</v>
+      <c r="D42" t="s">
+        <v>80</v>
+      </c>
+      <c r="E42" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1338,11 +1431,11 @@
       <c r="C43" t="s">
         <v>32</v>
       </c>
-      <c r="D43">
-        <v>2</v>
-      </c>
-      <c r="E43">
-        <v>2</v>
+      <c r="D43" t="s">
+        <v>82</v>
+      </c>
+      <c r="E43" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1355,11 +1448,11 @@
       <c r="C44" t="s">
         <v>32</v>
       </c>
-      <c r="D44">
-        <v>1</v>
-      </c>
-      <c r="E44">
-        <v>2</v>
+      <c r="D44" t="s">
+        <v>90</v>
+      </c>
+      <c r="E44" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1372,11 +1465,11 @@
       <c r="C45" t="s">
         <v>33</v>
       </c>
-      <c r="D45">
-        <v>2</v>
-      </c>
-      <c r="E45">
-        <v>2</v>
+      <c r="D45" t="s">
+        <v>91</v>
+      </c>
+      <c r="E45" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1389,11 +1482,11 @@
       <c r="C46" t="s">
         <v>33</v>
       </c>
-      <c r="D46">
-        <v>0</v>
-      </c>
-      <c r="E46">
-        <v>2</v>
+      <c r="D46" t="s">
+        <v>80</v>
+      </c>
+      <c r="E46" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1406,11 +1499,11 @@
       <c r="C47" t="s">
         <v>33</v>
       </c>
-      <c r="D47">
-        <v>0</v>
-      </c>
-      <c r="E47">
-        <v>1</v>
+      <c r="D47" t="s">
+        <v>80</v>
+      </c>
+      <c r="E47" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1423,11 +1516,11 @@
       <c r="C48" t="s">
         <v>34</v>
       </c>
-      <c r="D48">
-        <v>1</v>
-      </c>
-      <c r="E48">
-        <v>1</v>
+      <c r="D48" t="s">
+        <v>92</v>
+      </c>
+      <c r="E48" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -1440,11 +1533,11 @@
       <c r="C49" t="s">
         <v>34</v>
       </c>
-      <c r="D49">
-        <v>0</v>
-      </c>
-      <c r="E49">
-        <v>0</v>
+      <c r="D49" t="s">
+        <v>80</v>
+      </c>
+      <c r="E49" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1457,11 +1550,11 @@
       <c r="C50" t="s">
         <v>35</v>
       </c>
-      <c r="D50">
-        <v>1</v>
-      </c>
-      <c r="E50">
-        <v>1</v>
+      <c r="D50" t="s">
+        <v>93</v>
+      </c>
+      <c r="E50" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -1474,11 +1567,11 @@
       <c r="C51" t="s">
         <v>35</v>
       </c>
-      <c r="D51">
-        <v>0</v>
-      </c>
-      <c r="E51">
-        <v>1</v>
+      <c r="D51" t="s">
+        <v>80</v>
+      </c>
+      <c r="E51" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -1491,11 +1584,11 @@
       <c r="C52" t="s">
         <v>36</v>
       </c>
-      <c r="D52">
-        <v>1</v>
-      </c>
-      <c r="E52">
-        <v>1</v>
+      <c r="D52" t="s">
+        <v>88</v>
+      </c>
+      <c r="E52" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -1508,11 +1601,11 @@
       <c r="C53" t="s">
         <v>36</v>
       </c>
-      <c r="D53">
-        <v>0</v>
-      </c>
-      <c r="E53">
-        <v>1</v>
+      <c r="D53" t="s">
+        <v>80</v>
+      </c>
+      <c r="E53" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1525,11 +1618,11 @@
       <c r="C54" t="s">
         <v>69</v>
       </c>
-      <c r="D54">
-        <v>1</v>
-      </c>
-      <c r="E54">
-        <v>1</v>
+      <c r="D54" t="s">
+        <v>82</v>
+      </c>
+      <c r="E54" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -1542,11 +1635,11 @@
       <c r="C55" t="s">
         <v>37</v>
       </c>
-      <c r="D55">
-        <v>1</v>
-      </c>
-      <c r="E55">
-        <v>1</v>
+      <c r="D55" t="s">
+        <v>82</v>
+      </c>
+      <c r="E55" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -1559,11 +1652,11 @@
       <c r="C56" t="s">
         <v>38</v>
       </c>
-      <c r="D56">
-        <v>0</v>
-      </c>
-      <c r="E56">
-        <v>1</v>
+      <c r="D56" t="s">
+        <v>80</v>
+      </c>
+      <c r="E56" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -1576,11 +1669,11 @@
       <c r="C57" t="s">
         <v>38</v>
       </c>
-      <c r="D57">
-        <v>2</v>
-      </c>
-      <c r="E57">
-        <v>0</v>
+      <c r="D57" t="s">
+        <v>90</v>
+      </c>
+      <c r="E57" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -1593,11 +1686,11 @@
       <c r="C58" t="s">
         <v>70</v>
       </c>
-      <c r="D58">
-        <v>0</v>
-      </c>
-      <c r="E58">
-        <v>1</v>
+      <c r="D58" t="s">
+        <v>80</v>
+      </c>
+      <c r="E58" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -1610,11 +1703,11 @@
       <c r="C59" t="s">
         <v>38</v>
       </c>
-      <c r="D59">
-        <v>0</v>
-      </c>
-      <c r="E59">
-        <v>0</v>
+      <c r="D59" t="s">
+        <v>80</v>
+      </c>
+      <c r="E59" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -1627,11 +1720,11 @@
       <c r="C60" t="s">
         <v>70</v>
       </c>
-      <c r="D60">
-        <v>1</v>
-      </c>
-      <c r="E60">
-        <v>0</v>
+      <c r="D60" t="s">
+        <v>86</v>
+      </c>
+      <c r="E60" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -1644,11 +1737,11 @@
       <c r="C61" t="s">
         <v>39</v>
       </c>
-      <c r="D61">
-        <v>0</v>
-      </c>
-      <c r="E61">
-        <v>0</v>
+      <c r="D61" t="s">
+        <v>80</v>
+      </c>
+      <c r="E61" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -1661,11 +1754,11 @@
       <c r="C62" t="s">
         <v>77</v>
       </c>
-      <c r="D62">
-        <v>2</v>
-      </c>
-      <c r="E62">
-        <v>0</v>
+      <c r="D62" t="s">
+        <v>82</v>
+      </c>
+      <c r="E62" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -1678,11 +1771,11 @@
       <c r="C63" t="s">
         <v>41</v>
       </c>
-      <c r="D63">
-        <v>0</v>
-      </c>
-      <c r="E63">
-        <v>1</v>
+      <c r="D63" t="s">
+        <v>80</v>
+      </c>
+      <c r="E63" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -1695,11 +1788,11 @@
       <c r="C64" t="s">
         <v>41</v>
       </c>
-      <c r="D64">
-        <v>1</v>
-      </c>
-      <c r="E64">
-        <v>1</v>
+      <c r="D64" t="s">
+        <v>82</v>
+      </c>
+      <c r="E64" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -1712,11 +1805,11 @@
       <c r="C65" t="s">
         <v>41</v>
       </c>
-      <c r="D65">
-        <v>0</v>
-      </c>
-      <c r="E65">
-        <v>0</v>
+      <c r="D65" t="s">
+        <v>80</v>
+      </c>
+      <c r="E65" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -1729,11 +1822,11 @@
       <c r="C66" t="s">
         <v>71</v>
       </c>
-      <c r="D66">
-        <v>0</v>
-      </c>
-      <c r="E66">
-        <v>1</v>
+      <c r="D66" t="s">
+        <v>80</v>
+      </c>
+      <c r="E66" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -1746,11 +1839,11 @@
       <c r="C67" t="s">
         <v>42</v>
       </c>
-      <c r="D67">
-        <v>1</v>
-      </c>
-      <c r="E67">
-        <v>1</v>
+      <c r="D67" t="s">
+        <v>82</v>
+      </c>
+      <c r="E67" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -1763,11 +1856,11 @@
       <c r="C68" t="s">
         <v>43</v>
       </c>
-      <c r="D68">
-        <v>2</v>
-      </c>
-      <c r="E68">
-        <v>1</v>
+      <c r="D68" t="s">
+        <v>89</v>
+      </c>
+      <c r="E68" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -1780,11 +1873,11 @@
       <c r="C69" t="s">
         <v>43</v>
       </c>
-      <c r="D69">
-        <v>0</v>
-      </c>
-      <c r="E69">
-        <v>1</v>
+      <c r="D69" t="s">
+        <v>80</v>
+      </c>
+      <c r="E69" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -1797,11 +1890,11 @@
       <c r="C70" t="s">
         <v>44</v>
       </c>
-      <c r="D70">
-        <v>1</v>
-      </c>
-      <c r="E70">
-        <v>1</v>
+      <c r="D70" t="s">
+        <v>94</v>
+      </c>
+      <c r="E70" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -1814,11 +1907,11 @@
       <c r="C71" t="s">
         <v>44</v>
       </c>
-      <c r="D71">
-        <v>0</v>
-      </c>
-      <c r="E71">
-        <v>0</v>
+      <c r="D71" t="s">
+        <v>80</v>
+      </c>
+      <c r="E71" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -1831,11 +1924,11 @@
       <c r="C72" t="s">
         <v>45</v>
       </c>
-      <c r="D72">
-        <v>1</v>
-      </c>
-      <c r="E72">
-        <v>1</v>
+      <c r="D72" t="s">
+        <v>95</v>
+      </c>
+      <c r="E72" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -1848,11 +1941,11 @@
       <c r="C73" t="s">
         <v>45</v>
       </c>
-      <c r="D73">
-        <v>0</v>
-      </c>
-      <c r="E73">
-        <v>1</v>
+      <c r="D73" t="s">
+        <v>80</v>
+      </c>
+      <c r="E73" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -1865,11 +1958,11 @@
       <c r="C74" t="s">
         <v>72</v>
       </c>
-      <c r="D74">
-        <v>1</v>
-      </c>
-      <c r="E74">
-        <v>0</v>
+      <c r="D74" t="s">
+        <v>82</v>
+      </c>
+      <c r="E74" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -1882,11 +1975,11 @@
       <c r="C75" t="s">
         <v>48</v>
       </c>
-      <c r="D75">
-        <v>2</v>
-      </c>
-      <c r="E75">
-        <v>1</v>
+      <c r="D75" t="s">
+        <v>85</v>
+      </c>
+      <c r="E75" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -1899,11 +1992,11 @@
       <c r="C76" t="s">
         <v>73</v>
       </c>
-      <c r="D76">
-        <v>0</v>
-      </c>
-      <c r="E76">
-        <v>1</v>
+      <c r="D76" t="s">
+        <v>80</v>
+      </c>
+      <c r="E76" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -1916,11 +2009,11 @@
       <c r="C77" t="s">
         <v>73</v>
       </c>
-      <c r="D77">
-        <v>1</v>
-      </c>
-      <c r="E77">
-        <v>1</v>
+      <c r="D77" t="s">
+        <v>82</v>
+      </c>
+      <c r="E77" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -1933,11 +2026,11 @@
       <c r="C78" t="s">
         <v>49</v>
       </c>
-      <c r="D78">
-        <v>0</v>
-      </c>
-      <c r="E78">
-        <v>2</v>
+      <c r="D78" t="s">
+        <v>80</v>
+      </c>
+      <c r="E78" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -1950,11 +2043,11 @@
       <c r="C79" t="s">
         <v>49</v>
       </c>
-      <c r="D79">
-        <v>0</v>
-      </c>
-      <c r="E79">
-        <v>1</v>
+      <c r="D79" t="s">
+        <v>80</v>
+      </c>
+      <c r="E79" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -1967,11 +2060,11 @@
       <c r="C80" t="s">
         <v>74</v>
       </c>
-      <c r="D80">
-        <v>1</v>
-      </c>
-      <c r="E80">
-        <v>1</v>
+      <c r="D80" t="s">
+        <v>82</v>
+      </c>
+      <c r="E80" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -1984,11 +2077,11 @@
       <c r="C81" t="s">
         <v>50</v>
       </c>
-      <c r="D81">
-        <v>0</v>
-      </c>
-      <c r="E81">
-        <v>2</v>
+      <c r="D81" t="s">
+        <v>80</v>
+      </c>
+      <c r="E81" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -2001,11 +2094,11 @@
       <c r="C82" t="s">
         <v>50</v>
       </c>
-      <c r="D82">
-        <v>2</v>
-      </c>
-      <c r="E82">
-        <v>1</v>
+      <c r="D82" t="s">
+        <v>91</v>
+      </c>
+      <c r="E82" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -2018,11 +2111,11 @@
       <c r="C83" t="s">
         <v>51</v>
       </c>
-      <c r="D83">
-        <v>0</v>
-      </c>
-      <c r="E83">
-        <v>1</v>
+      <c r="D83" t="s">
+        <v>80</v>
+      </c>
+      <c r="E83" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -2035,11 +2128,11 @@
       <c r="C84" t="s">
         <v>51</v>
       </c>
-      <c r="D84">
-        <v>2</v>
-      </c>
-      <c r="E84">
-        <v>1</v>
+      <c r="D84" t="s">
+        <v>96</v>
+      </c>
+      <c r="E84" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -2052,11 +2145,11 @@
       <c r="C85" t="s">
         <v>78</v>
       </c>
-      <c r="D85">
-        <v>1</v>
-      </c>
-      <c r="E85">
-        <v>1</v>
+      <c r="D85" t="s">
+        <v>91</v>
+      </c>
+      <c r="E85" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -2069,11 +2162,11 @@
       <c r="C86" t="s">
         <v>53</v>
       </c>
-      <c r="D86">
-        <v>1</v>
-      </c>
-      <c r="E86">
-        <v>2</v>
+      <c r="D86" t="s">
+        <v>97</v>
+      </c>
+      <c r="E86" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -2086,11 +2179,11 @@
       <c r="C87" t="s">
         <v>54</v>
       </c>
-      <c r="D87">
-        <v>2</v>
-      </c>
-      <c r="E87">
-        <v>1</v>
+      <c r="D87" t="s">
+        <v>82</v>
+      </c>
+      <c r="E87" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -2103,11 +2196,11 @@
       <c r="C88" t="s">
         <v>55</v>
       </c>
-      <c r="D88">
-        <v>0</v>
-      </c>
-      <c r="E88">
-        <v>2</v>
+      <c r="D88" t="s">
+        <v>80</v>
+      </c>
+      <c r="E88" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -2120,11 +2213,11 @@
       <c r="C89" t="s">
         <v>55</v>
       </c>
-      <c r="D89">
-        <v>0</v>
-      </c>
-      <c r="E89">
-        <v>1</v>
+      <c r="D89" t="s">
+        <v>80</v>
+      </c>
+      <c r="E89" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -2137,11 +2230,11 @@
       <c r="C90" t="s">
         <v>56</v>
       </c>
-      <c r="D90">
-        <v>1</v>
-      </c>
-      <c r="E90">
-        <v>3</v>
+      <c r="D90" t="s">
+        <v>82</v>
+      </c>
+      <c r="E90" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -2154,11 +2247,11 @@
       <c r="C91" t="s">
         <v>56</v>
       </c>
-      <c r="D91">
-        <v>0</v>
-      </c>
-      <c r="E91">
-        <v>2</v>
+      <c r="D91" t="s">
+        <v>80</v>
+      </c>
+      <c r="E91" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -2171,11 +2264,11 @@
       <c r="C92" t="s">
         <v>56</v>
       </c>
-      <c r="D92">
-        <v>1</v>
-      </c>
-      <c r="E92">
-        <v>2</v>
+      <c r="D92" t="s">
+        <v>82</v>
+      </c>
+      <c r="E92" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -2188,11 +2281,11 @@
       <c r="C93" t="s">
         <v>57</v>
       </c>
-      <c r="D93">
-        <v>2</v>
-      </c>
-      <c r="E93">
-        <v>1</v>
+      <c r="D93" t="s">
+        <v>93</v>
+      </c>
+      <c r="E93" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -2205,11 +2298,11 @@
       <c r="C94" t="s">
         <v>57</v>
       </c>
-      <c r="D94">
-        <v>0</v>
-      </c>
-      <c r="E94">
-        <v>1</v>
+      <c r="D94" t="s">
+        <v>80</v>
+      </c>
+      <c r="E94" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -2222,11 +2315,11 @@
       <c r="C95" t="s">
         <v>59</v>
       </c>
-      <c r="D95">
-        <v>1</v>
-      </c>
-      <c r="E95">
-        <v>1</v>
+      <c r="D95" t="s">
+        <v>82</v>
+      </c>
+      <c r="E95" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -2239,11 +2332,11 @@
       <c r="C96" t="s">
         <v>60</v>
       </c>
-      <c r="D96">
-        <v>1</v>
-      </c>
-      <c r="E96">
-        <v>2</v>
+      <c r="D96" t="s">
+        <v>82</v>
+      </c>
+      <c r="E96" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -2256,11 +2349,11 @@
       <c r="C97" t="s">
         <v>61</v>
       </c>
-      <c r="D97">
-        <v>1</v>
-      </c>
-      <c r="E97">
-        <v>1</v>
+      <c r="D97" t="s">
+        <v>82</v>
+      </c>
+      <c r="E97" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -2273,11 +2366,11 @@
       <c r="C98" t="s">
         <v>75</v>
       </c>
-      <c r="D98">
-        <v>1</v>
-      </c>
-      <c r="E98">
-        <v>1</v>
+      <c r="D98" t="s">
+        <v>82</v>
+      </c>
+      <c r="E98" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -2290,11 +2383,11 @@
       <c r="C99" t="s">
         <v>75</v>
       </c>
-      <c r="D99">
-        <v>1</v>
-      </c>
-      <c r="E99">
-        <v>0</v>
+      <c r="D99" t="s">
+        <v>82</v>
+      </c>
+      <c r="E99" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -2307,11 +2400,11 @@
       <c r="C100" t="s">
         <v>79</v>
       </c>
-      <c r="D100">
-        <v>0</v>
-      </c>
-      <c r="E100">
-        <v>1</v>
+      <c r="D100" t="s">
+        <v>80</v>
+      </c>
+      <c r="E100" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/simulation_data/tuesday_afternoon.xlsx
+++ b/simulation_data/tuesday_afternoon.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:H100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,6 +464,11 @@
           <t>system_time_min</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>service_type</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -493,6 +498,11 @@
       <c r="G2" t="n">
         <v>3.156627008463399</v>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -522,6 +532,11 @@
       <c r="G3" t="n">
         <v>2.874062143568314</v>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,6 +566,11 @@
       <c r="G4" t="n">
         <v>1.993316141012463</v>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -580,6 +600,11 @@
       <c r="G5" t="n">
         <v>1.965571520704819</v>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -609,6 +634,11 @@
       <c r="G6" t="n">
         <v>2.941277102561688</v>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -638,6 +668,11 @@
       <c r="G7" t="n">
         <v>2.115798754027925</v>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -667,6 +702,11 @@
       <c r="G8" t="n">
         <v>2.481894657496674</v>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -696,6 +736,11 @@
       <c r="G9" t="n">
         <v>2.646046128855427</v>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -725,6 +770,11 @@
       <c r="G10" t="n">
         <v>1.454126831938167</v>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -754,6 +804,11 @@
       <c r="G11" t="n">
         <v>1.989597086078096</v>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -783,6 +838,11 @@
       <c r="G12" t="n">
         <v>2.491070554921698</v>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -812,6 +872,11 @@
       <c r="G13" t="n">
         <v>2.748727450555899</v>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -841,6 +906,11 @@
       <c r="G14" t="n">
         <v>3.151253777960386</v>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -870,6 +940,11 @@
       <c r="G15" t="n">
         <v>2.582286088768825</v>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -899,6 +974,11 @@
       <c r="G16" t="n">
         <v>2.175581990226312</v>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -928,6 +1008,11 @@
       <c r="G17" t="n">
         <v>1.209224363954406</v>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -957,6 +1042,11 @@
       <c r="G18" t="n">
         <v>1.085672233508653</v>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -986,6 +1076,11 @@
       <c r="G19" t="n">
         <v>2.743449851315673</v>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1015,6 +1110,11 @@
       <c r="G20" t="n">
         <v>1.306149485783636</v>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1044,6 +1144,11 @@
       <c r="G21" t="n">
         <v>2.599350896030714</v>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1073,6 +1178,11 @@
       <c r="G22" t="n">
         <v>2.644905396615283</v>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1102,6 +1212,11 @@
       <c r="G23" t="n">
         <v>2.800501570902007</v>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1131,6 +1246,11 @@
       <c r="G24" t="n">
         <v>2.155748366475881</v>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1160,6 +1280,11 @@
       <c r="G25" t="n">
         <v>3.278593711558811</v>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1189,6 +1314,11 @@
       <c r="G26" t="n">
         <v>2.16351377486856</v>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1218,6 +1348,11 @@
       <c r="G27" t="n">
         <v>1.825843822663635</v>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1247,6 +1382,11 @@
       <c r="G28" t="n">
         <v>3.416401346198847</v>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1276,6 +1416,11 @@
       <c r="G29" t="n">
         <v>3.071387774909834</v>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1305,6 +1450,11 @@
       <c r="G30" t="n">
         <v>2.499108757163585</v>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1334,6 +1484,11 @@
       <c r="G31" t="n">
         <v>2.786746201138242</v>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1363,6 +1518,11 @@
       <c r="G32" t="n">
         <v>2.02678859505985</v>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1392,6 +1552,11 @@
       <c r="G33" t="n">
         <v>2.690040417658427</v>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1421,6 +1586,11 @@
       <c r="G34" t="n">
         <v>1.946770918681797</v>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1450,6 +1620,11 @@
       <c r="G35" t="n">
         <v>3.819786149428217</v>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1479,6 +1654,11 @@
       <c r="G36" t="n">
         <v>4.597543058169504</v>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1508,6 +1688,11 @@
       <c r="G37" t="n">
         <v>4.275399552860989</v>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1537,6 +1722,11 @@
       <c r="G38" t="n">
         <v>1.710893329544203</v>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1566,6 +1756,11 @@
       <c r="G39" t="n">
         <v>1.441205779868402</v>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1595,6 +1790,11 @@
       <c r="G40" t="n">
         <v>1.858376945044564</v>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1624,6 +1824,11 @@
       <c r="G41" t="n">
         <v>2.635466191642814</v>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1653,6 +1858,11 @@
       <c r="G42" t="n">
         <v>4.14622725690575</v>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1682,6 +1892,11 @@
       <c r="G43" t="n">
         <v>3.852488499213184</v>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1711,6 +1926,11 @@
       <c r="G44" t="n">
         <v>3.846045269682294</v>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1740,6 +1960,11 @@
       <c r="G45" t="n">
         <v>2.736121625600648</v>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1769,6 +1994,11 @@
       <c r="G46" t="n">
         <v>2.719969149435568</v>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1798,6 +2028,11 @@
       <c r="G47" t="n">
         <v>2.56368390964351</v>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1827,6 +2062,11 @@
       <c r="G48" t="n">
         <v>1.67900241501128</v>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1856,6 +2096,11 @@
       <c r="G49" t="n">
         <v>2.477232489622332</v>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1885,6 +2130,11 @@
       <c r="G50" t="n">
         <v>2.839576814814052</v>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1914,6 +2164,11 @@
       <c r="G51" t="n">
         <v>2.020049445934696</v>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1943,6 +2198,11 @@
       <c r="G52" t="n">
         <v>2.641864184227025</v>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1972,6 +2232,11 @@
       <c r="G53" t="n">
         <v>2.614596935152412</v>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2001,6 +2266,11 @@
       <c r="G54" t="n">
         <v>1.892410259410524</v>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2030,6 +2300,11 @@
       <c r="G55" t="n">
         <v>2.23228303472166</v>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2059,6 +2334,11 @@
       <c r="G56" t="n">
         <v>3.046385399158846</v>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2088,6 +2368,11 @@
       <c r="G57" t="n">
         <v>0.8817847478976532</v>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2117,6 +2402,11 @@
       <c r="G58" t="n">
         <v>2.729132067904041</v>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2146,6 +2436,11 @@
       <c r="G59" t="n">
         <v>1.367932784819784</v>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2175,6 +2470,11 @@
       <c r="G60" t="n">
         <v>1.610375252432163</v>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2204,6 +2504,11 @@
       <c r="G61" t="n">
         <v>1.891981993546393</v>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2233,6 +2538,11 @@
       <c r="G62" t="n">
         <v>1.902574034180262</v>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2262,6 +2572,11 @@
       <c r="G63" t="n">
         <v>1.966371284105171</v>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2291,6 +2606,11 @@
       <c r="G64" t="n">
         <v>0.866455591991877</v>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2320,6 +2640,11 @@
       <c r="G65" t="n">
         <v>1.946757291432783</v>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2349,6 +2674,11 @@
       <c r="G66" t="n">
         <v>2.356976373528442</v>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2378,6 +2708,11 @@
       <c r="G67" t="n">
         <v>2.712974497225837</v>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2407,6 +2742,11 @@
       <c r="G68" t="n">
         <v>0.6542773920988637</v>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2436,6 +2776,11 @@
       <c r="G69" t="n">
         <v>0.8988797821176845</v>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2465,6 +2810,11 @@
       <c r="G70" t="n">
         <v>1.093185947182749</v>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2494,6 +2844,11 @@
       <c r="G71" t="n">
         <v>1.969411695079683</v>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2523,6 +2878,11 @@
       <c r="G72" t="n">
         <v>0.9689092285964968</v>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2552,6 +2912,11 @@
       <c r="G73" t="n">
         <v>0.9725533330806819</v>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2581,6 +2946,11 @@
       <c r="G74" t="n">
         <v>1.629618398715465</v>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2610,6 +2980,11 @@
       <c r="G75" t="n">
         <v>2.458502343767214</v>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2639,6 +3014,11 @@
       <c r="G76" t="n">
         <v>4.073663674127737</v>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2668,6 +3048,11 @@
       <c r="G77" t="n">
         <v>2.129943463562903</v>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2697,6 +3082,11 @@
       <c r="G78" t="n">
         <v>3.316824757109792</v>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2726,6 +3116,11 @@
       <c r="G79" t="n">
         <v>2.545446549713478</v>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2755,6 +3150,11 @@
       <c r="G80" t="n">
         <v>3.133746761628294</v>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2784,6 +3184,11 @@
       <c r="G81" t="n">
         <v>4.89772696987842</v>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2813,6 +3218,11 @@
       <c r="G82" t="n">
         <v>2.35551846171306</v>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2842,6 +3252,11 @@
       <c r="G83" t="n">
         <v>2.459736621061437</v>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2871,6 +3286,11 @@
       <c r="G84" t="n">
         <v>1.64947660896009</v>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2900,6 +3320,11 @@
       <c r="G85" t="n">
         <v>3.044571970218405</v>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2929,6 +3354,11 @@
       <c r="G86" t="n">
         <v>2.318767548162792</v>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2958,6 +3388,11 @@
       <c r="G87" t="n">
         <v>0.809044305226182</v>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2987,6 +3422,11 @@
       <c r="G88" t="n">
         <v>2.453090552803117</v>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3016,6 +3456,11 @@
       <c r="G89" t="n">
         <v>1.578389088252982</v>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3045,6 +3490,11 @@
       <c r="G90" t="n">
         <v>3.221857877953101</v>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3074,6 +3524,11 @@
       <c r="G91" t="n">
         <v>2.495774062869782</v>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3103,6 +3558,11 @@
       <c r="G92" t="n">
         <v>2.612971458622461</v>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3132,6 +3592,11 @@
       <c r="G93" t="n">
         <v>1.546288326108155</v>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3161,6 +3626,11 @@
       <c r="G94" t="n">
         <v>1.568282036481916</v>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3190,6 +3660,11 @@
       <c r="G95" t="n">
         <v>2.345955726461184</v>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3219,6 +3694,11 @@
       <c r="G96" t="n">
         <v>1.942992652302287</v>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3248,6 +3728,11 @@
       <c r="G97" t="n">
         <v>2.501887847346498</v>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3277,6 +3762,11 @@
       <c r="G98" t="n">
         <v>1.797413931559904</v>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3306,6 +3796,11 @@
       <c r="G99" t="n">
         <v>1.492795976149893</v>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3334,6 +3829,11 @@
       </c>
       <c r="G100" t="n">
         <v>2.652332029161269</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
       </c>
     </row>
   </sheetData>
